--- a/artfynd/A 41685-2026 artfynd.xlsx
+++ b/artfynd/A 41685-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137294722</v>
       </c>
       <c r="B2" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,49 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137294721</v>
+        <v>137329879</v>
       </c>
       <c r="B3" t="n">
-        <v>58030</v>
+        <v>80049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sikån, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757191</v>
+        <v>757105</v>
       </c>
       <c r="R3" t="n">
-        <v>7162151</v>
+        <v>7162232</v>
       </c>
       <c r="S3" t="n">
         <v>29</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,69 +887,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294721</t>
+          <t>https://artportalen.se/Sighting/137329879</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137294728</v>
+        <v>137329875</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sikån, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757143</v>
+        <v>757189</v>
       </c>
       <c r="R4" t="n">
-        <v>7162301</v>
+        <v>7162064</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,69 +999,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294728</t>
+          <t>https://artportalen.se/Sighting/137329875</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137294731</v>
+        <v>137329876</v>
       </c>
       <c r="B5" t="n">
-        <v>58030</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sikån, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>757350</v>
+        <v>757098</v>
       </c>
       <c r="R5" t="n">
-        <v>7162237</v>
+        <v>7162210</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,66 +1111,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294731</t>
+          <t>https://artportalen.se/Sighting/137329876</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137294727</v>
+        <v>137329883</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>80522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sikån, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757114</v>
+        <v>757327</v>
       </c>
       <c r="R6" t="n">
-        <v>7162238</v>
+        <v>7162295</v>
       </c>
       <c r="S6" t="n">
         <v>43</v>
@@ -1229,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,12 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Barksprätt spår på gran</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,16 +1223,968 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329883</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137294721</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>757191</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7162151</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294721</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137294728</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>757143</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7162301</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294728</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137294731</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>757350</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7162237</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294731</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137329874</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>757169</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7162075</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rotsockelhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329874</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137329877</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>757078</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7162207</v>
+      </c>
+      <c r="S11" t="n">
+        <v>16</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födohack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329877</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137329878</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>757085</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7162205</v>
+      </c>
+      <c r="S12" t="n">
+        <v>26</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rotsockelhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329878</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137329882</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>757261</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7162372</v>
+      </c>
+      <c r="S13" t="n">
+        <v>24</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födohack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329882</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137294727</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>757114</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7162238</v>
+      </c>
+      <c r="S14" t="n">
+        <v>43</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Barksprätt spår på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137294727</t>
         </is>
@@ -1281,6 +2197,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41685-2026 artfynd.xlsx
+++ b/artfynd/A 41685-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137294722</v>
       </c>
       <c r="B2" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137329879</v>
       </c>
       <c r="B3" t="n">
-        <v>80049</v>
+        <v>80052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137329875</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137329876</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137329883</v>
       </c>
       <c r="B6" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137294721</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137294728</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>137294731</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137329874</v>
       </c>
       <c r="B10" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>137329877</v>
       </c>
       <c r="B11" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>137329878</v>
       </c>
       <c r="B12" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>137329882</v>
       </c>
       <c r="B13" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137294727</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 41685-2026 artfynd.xlsx
+++ b/artfynd/A 41685-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137294722</v>
       </c>
       <c r="B2" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41685-2026 artfynd.xlsx
+++ b/artfynd/A 41685-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137294722</v>
+        <v>137396946</v>
       </c>
       <c r="B2" t="n">
-        <v>92596</v>
+        <v>92742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sikån, Vb</t>
+          <t>Sikforsen, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>757133</v>
+        <v>757037</v>
       </c>
       <c r="R2" t="n">
-        <v>7162078</v>
+        <v>7162237</v>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +755,14 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:28</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ca 3 meter upp på gammal sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,55 +771,56 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294722</t>
+          <t>https://artportalen.se/Sighting/137396946</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137329879</v>
+        <v>137294722</v>
       </c>
       <c r="B3" t="n">
-        <v>80052</v>
+        <v>92601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1353</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757105</v>
+        <v>757133</v>
       </c>
       <c r="R3" t="n">
-        <v>7162232</v>
+        <v>7162078</v>
       </c>
       <c r="S3" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,65 +890,72 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329879</t>
+          <t>https://artportalen.se/Sighting/137294722</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137329875</v>
+        <v>137396727</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>92601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sikån, Vb</t>
+          <t>Sikfosen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757189</v>
+        <v>757132</v>
       </c>
       <c r="R4" t="n">
-        <v>7162064</v>
+        <v>7162071</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,92 +982,90 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329875</t>
+          <t>https://artportalen.se/Sighting/137396727</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137329876</v>
+        <v>137396531</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>83389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sikån, Vb</t>
+          <t>Sikforsen, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>757098</v>
+        <v>757149</v>
       </c>
       <c r="R5" t="n">
-        <v>7162210</v>
+        <v>7162053</v>
       </c>
       <c r="S5" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,76 +1092,67 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:47</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:47</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329876</t>
+          <t>https://artportalen.se/Sighting/137396531</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137329883</v>
+        <v>137329879</v>
       </c>
       <c r="B6" t="n">
-        <v>80525</v>
+        <v>80057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757327</v>
+        <v>757105</v>
       </c>
       <c r="R6" t="n">
-        <v>7162295</v>
+        <v>7162232</v>
       </c>
       <c r="S6" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,58 +1233,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329883</t>
+          <t>https://artportalen.se/Sighting/137329879</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137294721</v>
+        <v>137329875</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sikån, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>757191</v>
+        <v>757189</v>
       </c>
       <c r="R7" t="n">
-        <v>7162151</v>
+        <v>7162064</v>
       </c>
       <c r="S7" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,12 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,69 +1334,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294721</t>
+          <t>https://artportalen.se/Sighting/137329875</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137294728</v>
+        <v>137329876</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sikån, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757143</v>
+        <v>757098</v>
       </c>
       <c r="R8" t="n">
-        <v>7162301</v>
+        <v>7162210</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,12 +1431,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,66 +1446,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294728</t>
+          <t>https://artportalen.se/Sighting/137329876</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137294731</v>
+        <v>137396322</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sikån, Vb</t>
+          <t>Sikforsen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757350</v>
+        <v>757165</v>
       </c>
       <c r="R9" t="n">
-        <v>7162237</v>
+        <v>7162074</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,97 +1538,90 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137294731</t>
+          <t>https://artportalen.se/Sighting/137396322</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137329874</v>
+        <v>137396368</v>
       </c>
       <c r="B10" t="n">
-        <v>58031</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sikån, Vb</t>
+          <t>Sikforsen, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>757169</v>
+        <v>757177</v>
       </c>
       <c r="R10" t="n">
-        <v>7162075</v>
+        <v>7162069</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1671,97 +1648,90 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rotsockelhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329874</t>
+          <t>https://artportalen.se/Sighting/137396368</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137329877</v>
+        <v>137396421</v>
       </c>
       <c r="B11" t="n">
-        <v>58031</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sikån, Vb</t>
+          <t>Sikforsen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>757078</v>
+        <v>757167</v>
       </c>
       <c r="R11" t="n">
-        <v>7162207</v>
+        <v>7162039</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,97 +1758,90 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födohack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329877</t>
+          <t>https://artportalen.se/Sighting/137396421</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137329878</v>
+        <v>137396933</v>
       </c>
       <c r="B12" t="n">
-        <v>58031</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sikån, Vb</t>
+          <t>Sikforsen, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>757085</v>
+        <v>756974</v>
       </c>
       <c r="R12" t="n">
-        <v>7162205</v>
+        <v>7162234</v>
       </c>
       <c r="S12" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,59 +1868,45 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rotsockelhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329878</t>
+          <t>https://artportalen.se/Sighting/137396933</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137329882</v>
+        <v>137396366</v>
       </c>
       <c r="B13" t="n">
-        <v>58031</v>
+        <v>83495</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,37 +1914,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sikån, Vb</t>
+          <t>Sikforsen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>757261</v>
+        <v>757173</v>
       </c>
       <c r="R13" t="n">
-        <v>7162372</v>
+        <v>7162070</v>
       </c>
       <c r="S13" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2022,98 +1978,80 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födohack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137329882</t>
+          <t>https://artportalen.se/Sighting/137396366</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137294727</v>
+        <v>137329883</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>80530</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sikån, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>757114</v>
+        <v>757327</v>
       </c>
       <c r="R14" t="n">
-        <v>7162238</v>
+        <v>7162295</v>
       </c>
       <c r="S14" t="n">
         <v>43</v>
@@ -2145,7 +2083,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,12 +2093,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Barksprätt spår på gran</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,18 +2108,1750 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137329883</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137396953</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80641</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sikforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>757037</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7162237</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137396953</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137294721</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>757191</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7162151</v>
+      </c>
+      <c r="S16" t="n">
+        <v>29</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294721</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137294728</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>757143</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7162301</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294728</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137294731</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>757350</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7162237</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137294731</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137329874</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>757169</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7162075</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rotsockelhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329874</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137329877</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>757078</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7162207</v>
+      </c>
+      <c r="S20" t="n">
+        <v>16</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födohack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329877</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137329878</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>757085</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7162205</v>
+      </c>
+      <c r="S21" t="n">
+        <v>26</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rotsockelhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329878</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137329882</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>757261</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7162372</v>
+      </c>
+      <c r="S22" t="n">
+        <v>24</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födohack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137329882</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137396902</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sikforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>757065</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7162185</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hål hackat i en gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137396902</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137396912</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sikforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>757062</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7162178</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hål hackat i gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137396912</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137396929</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sikforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>756990</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7162141</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hackade hål</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137396929</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137294727</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>757114</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7162238</v>
+      </c>
+      <c r="S26" t="n">
+        <v>43</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Barksprätt spår på gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137294727</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137396544</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sikforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>757147</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7162056</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137396544</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137396744</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sikforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>757077</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7162177</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137396744</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137396732</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92561</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sikfosen, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>757132</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7162071</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>på samma granlåga som rynkskinn</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137396732</t>
         </is>
       </c>
     </row>
@@ -2205,6 +3870,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41685-2026 artfynd.xlsx
+++ b/artfynd/A 41685-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137396946</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137294722</v>
       </c>
       <c r="B3" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137396727</v>
       </c>
       <c r="B4" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137396531</v>
       </c>
       <c r="B5" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137329879</v>
       </c>
       <c r="B6" t="n">
-        <v>80057</v>
+        <v>80068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137329875</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137329876</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137396322</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>137396368</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>137396421</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137396933</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137396366</v>
       </c>
       <c r="B13" t="n">
-        <v>83495</v>
+        <v>83506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137329883</v>
       </c>
       <c r="B14" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137396953</v>
       </c>
       <c r="B15" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>137396732</v>
       </c>
       <c r="B29" t="n">
-        <v>92561</v>
+        <v>92573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41685-2026 artfynd.xlsx
+++ b/artfynd/A 41685-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137396946</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137294722</v>
       </c>
       <c r="B3" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137396727</v>
       </c>
       <c r="B4" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137396531</v>
       </c>
       <c r="B5" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137329879</v>
       </c>
       <c r="B6" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137329875</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137329876</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137396322</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>137396368</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>137396421</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137396933</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137396366</v>
       </c>
       <c r="B13" t="n">
-        <v>83506</v>
+        <v>83507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137329883</v>
       </c>
       <c r="B14" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137396953</v>
       </c>
       <c r="B15" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>137396732</v>
       </c>
       <c r="B29" t="n">
-        <v>92573</v>
+        <v>92574</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41685-2026 artfynd.xlsx
+++ b/artfynd/A 41685-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137396946</v>
       </c>
       <c r="B2" t="n">
-        <v>92755</v>
+        <v>92758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137294722</v>
       </c>
       <c r="B3" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137396727</v>
       </c>
       <c r="B4" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137396531</v>
       </c>
       <c r="B5" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137329879</v>
       </c>
       <c r="B6" t="n">
-        <v>80069</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137329875</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137329876</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137396322</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>137396368</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>137396421</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137396933</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137396366</v>
       </c>
       <c r="B13" t="n">
-        <v>83507</v>
+        <v>83509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137329883</v>
       </c>
       <c r="B14" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137396953</v>
       </c>
       <c r="B15" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>137396732</v>
       </c>
       <c r="B29" t="n">
-        <v>92574</v>
+        <v>92577</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41685-2026 artfynd.xlsx
+++ b/artfynd/A 41685-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137396946</v>
       </c>
       <c r="B2" t="n">
-        <v>92758</v>
+        <v>92762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137294722</v>
       </c>
       <c r="B3" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>137396727</v>
       </c>
       <c r="B4" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137396531</v>
       </c>
       <c r="B5" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>137329879</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137329875</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>137329876</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>137396322</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>137396368</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>137396421</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>137396933</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>137396366</v>
       </c>
       <c r="B13" t="n">
-        <v>83509</v>
+        <v>83513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>137329883</v>
       </c>
       <c r="B14" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137396953</v>
       </c>
       <c r="B15" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>137294721</v>
       </c>
       <c r="B16" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>137294728</v>
       </c>
       <c r="B17" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137294731</v>
       </c>
       <c r="B18" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>137329874</v>
       </c>
       <c r="B19" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137329877</v>
       </c>
       <c r="B20" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>137329878</v>
       </c>
       <c r="B21" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>137329882</v>
       </c>
       <c r="B22" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>137396902</v>
       </c>
       <c r="B23" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>137396912</v>
       </c>
       <c r="B24" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>137396929</v>
       </c>
       <c r="B25" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>137294727</v>
       </c>
       <c r="B26" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137396544</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>137396744</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>137396732</v>
       </c>
       <c r="B29" t="n">
-        <v>92577</v>
+        <v>92581</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
